--- a/QCM3_1_CH.xlsx
+++ b/QCM3_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8B51EC-DF93-44E0-8D5D-97E64416BA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6889125-5CFB-47B2-B5A6-386355AD4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,33 +266,12 @@
     <t>A l'équilibre la masse de cadmium a doublé.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Mélange de Cadmium - Fer&lt;/b&gt;/center&gt;&lt;br&gt;
-On prépare la solution aqueuse S en mélangeant :
-&lt;br&gt; * 0,28 g de poudre de fer Fe ;
-&lt;br&gt; * 0,56 g de cadmium Cd ;
-&lt;br&gt; * 10 mL d'une solution aqueuse de sulfate de fer (II) de concentration molaire en soluté apporté $1,0.10^{-1}$ mol/L ($Fe^{2+}_{(aq)} + SO^{2-}_{4(aq)}$) ;
-&lt;br&gt; * 10 mL d'une solution aqueuse de chlorure de cadmium de concentration molaire en soluté apporté $1,0.10^{-1}$ mol/L ($Cd^{2+}_{(aq)} + 2Cl^-_{(aq)}$).
-&lt;br&gt;La transformation est modélisée par l'équation chimique : 
-&lt;br&gt;$Cd^{2+}_{(aq)} + Fe_{(s)} \rightarrow Cd_{(s)} + Fe^{2+}_{(aq)}$.
-&lt;br&gt;On donne, à 25°C la constante de cette réaction : K = 20. $\quad$ $21 \times 0,90 = 19$</t>
-  </si>
-  <si>
     <t>A l'équilibre, on ajoute au système S précédent quelques cristaux de chlorure de cadmium. On obtient le mélange S'.
 &lt;br&gt;Le système chimique évolue spontanément dans le sens de l'équation ci-dessus :</t>
   </si>
   <si>
     <t>Au nouvel équilibre, on ajoute au mélange S' précédent un peu de poudre de fer.
 &lt;br&gt;Le système chimique reste :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La réaction entre le cuivre et le dibrome &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Pour étudier la réaction entre le cuivre et le dibrome en solution, on place dans un bécher :
-br&gt; * Le volume V_1 = 50 mL d'une solution de bromure de cuivre II ($Cu^{2+}_{(aq)} + 2Br^-_{(aq)}$) de concentration molaire C_1 = $4.10^{-2}$ mol/L ;
-&lt;br&gt; * Le volume V_2 = 50 mL d'une solution de dibrome $Br_{2(aq)}$ de concentration molaire C_2 = $4.10^{-2}$ mol/L ;
-&lt;br&gt; *- La poudre de cuivre.
-&lt;br&gt;Données : 
-Constante d'équilibre associée à l'équation $Br_{2(aq)} + Cu_{(s)} \rightleftharpoons 2Br^-_{(aq)} + Cu^{2+}_{(aq)}$ : $K = 1,2.10^{25}$
-- Le cuivre en excès.</t>
   </si>
   <si>
     <t>$Br^-_{(aq)} / Br_{2(aq)}$ et $Cu^{2+}_{(aq)} / Cu_{(s)}$</t>
@@ -726,12 +705,33 @@
 &lt;br&gt;$\sqrt{10^{-5}} = 3,2.10^{-3}$ ; $1/\sqrt{50} = 0,14$ ; $\sqrt{50} = 7,07$</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;La pile (Plomb/Cuivre)&lt;/b&gt;/center&gt;&lt;br&gt;
+    <t>&lt;center&gt;&lt;b&gt;La pile (Plomb/Cuivre)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 &lt;br&gt;Une lame de plomb Pb de masse totale 100,0 g est à demi immergée dans une solution aqueuse de sulfate de plomb ($Pb^{2+}_{(aq)} + SO^{2-}_{4(aq)}$).
 &lt;br&gt;Une lame de cuivre Cu de masse totale 100,0 g est à demi immergée, de même, dans une solution aqueuse de sulfate de cuivre ($Cu^{2+}_{(aq)} + SO^{2-}_{4(aq)}$).
 &lt;br&gt;Les demi-piles ainsi constituées sont reliées par un pont électrolytique contenant une solution aqueuse de nitrate de potassium ($K^+_{(aq)} + NO^-_{3(aq)}$). On réalise alors le circuit schématisé ci-dessous. L'ampèremètre indique que le courant dans le circuit extérieur circule de la lame de cuivre vers la lame de plomb.
 &lt;br&gt;Données : 
 &lt;br&gt;Couples redox intervenant dans la pile : $Cu^{2+}_{(aq)}/Cu_{(s)}$, $Pb^{2+}_{(aq)}/Pb_{(s)}$. $\quad$ 1 Faraday : $F \approx 1,0.10^5$ C/mol. $\quad$ $M(Pb) = 207,2$ g/mol.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La réaction entre le cuivre et le dibrome &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Pour étudier la réaction entre le cuivre et le dibrome en solution, on place dans un bécher :
+&lt;br&gt; * Le volume V_1 = 50 mL d'une solution de bromure de cuivre II ($Cu^{2+}_{(aq)} + 2Br^-_{(aq)}$) de concentration molaire C_1 = $4.10^{-2}$ mol/L ;
+&lt;br&gt; * Le volume V_2 = 50 mL d'une solution de dibrome $Br_{2(aq)}$ de concentration molaire C_2 = $4.10^{-2}$ mol/L ;
+&lt;br&gt; * La poudre de cuivre.
+&lt;br&gt;Données : 
+&lt;br&gt;Constante d'équilibre associée à l'équation $Br_{2(aq)} + Cu_{(s)} \rightleftharpoons 2Br^-_{(aq)} + Cu^{2+}_{(aq)}$ : $K = 1,2.10^{25}$
+- Le cuivre en excès.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Mélange de Cadmium - Fer&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On prépare la solution aqueuse S en mélangeant :
+&lt;br&gt; * 0,28 g de poudre de fer Fe ;
+&lt;br&gt; * 0,56 g de cadmium Cd ;
+&lt;br&gt; * 10 mL d'une solution aqueuse de sulfate de fer (II) ($Fe^{2+}_{(aq)} + SO^{2-}_{4(aq)}$) de concentration molaire en soluté apporté $1,0.10^{-1}$ mol/L  ;
+&lt;br&gt; * 10 mL d'une solution aqueuse de chlorure de cadmium ($Cd^{2+}_{(aq)} + 2Cl^-_{(aq)}$) de concentration molaire en soluté apporté $1,0.10^{-1}$ mol/L.
+&lt;br&gt;La transformation est modélisée par l'équation chimique : 
+&lt;br&gt;$Cd^{2+}_{(aq)} + Fe_{(s)} \rightarrow Cd_{(s)} + Fe^{2+}_{(aq)}$.
+&lt;br&gt;On donne, à 25°C la constante de cette réaction : K = 20. $\quad$ $21 \times 0,90 = 19$</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>65</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="6" spans="1:11" ht="285">
       <c r="A6" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>70</v>
@@ -1452,7 +1452,7 @@
         <v>28</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -1537,9 +1537,9 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="242.25">
+    <row r="10" spans="1:11" ht="270.75">
       <c r="A10" s="11" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>74</v>
@@ -1596,7 +1596,7 @@
     <row r="12" spans="1:11" ht="71.25">
       <c r="A12" s="11"/>
       <c r="B12" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
@@ -1623,7 +1623,7 @@
     <row r="13" spans="1:11" ht="42.75">
       <c r="A13" s="11"/>
       <c r="B13" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>3</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="14" spans="1:11" ht="228">
       <c r="A14" s="11" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
@@ -1663,10 +1663,10 @@
         <v>59</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>59</v>
@@ -1677,7 +1677,7 @@
     <row r="15" spans="1:11">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>3</v>
@@ -1705,549 +1705,549 @@
     </row>
     <row r="16" spans="1:11" ht="213.75">
       <c r="A16" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="G16" s="14" t="s">
         <v>85</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>87</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>89</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>91</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="15"/>
       <c r="B18" s="16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="G18" s="18" t="s">
         <v>93</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>95</v>
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15"/>
       <c r="B19" s="16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="G19" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>99</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>99</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="228">
       <c r="A21" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="G21" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>103</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="G22" s="18" t="s">
         <v>105</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>107</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.5">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="G23" s="18" t="s">
         <v>109</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>111</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="G24" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>115</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="313.5">
       <c r="A25" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>173</v>
-      </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="G25" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>119</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.5">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="G26" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>123</v>
       </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="42.75">
       <c r="A27" s="15"/>
       <c r="B27" s="16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="G27" s="18" t="s">
         <v>125</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="H27" s="18"/>
       <c r="I27" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="G28" s="18" t="s">
         <v>129</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>131</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="15"/>
       <c r="B29" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="G29" s="18" t="s">
         <v>133</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>135</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="199.5">
       <c r="A30" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="G30" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>139</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.5">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="G31" s="18" t="s">
         <v>141</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>143</v>
       </c>
       <c r="H31" s="18"/>
       <c r="I31" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="28.5">
       <c r="A32" s="15"/>
       <c r="B32" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="G32" s="18" t="s">
         <v>145</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>147</v>
       </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="15"/>
       <c r="B33" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="G33" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>151</v>
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="185.25">
       <c r="A34" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="15"/>
       <c r="B35" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="G35" s="18" t="s">
         <v>155</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>157</v>
       </c>
       <c r="H35" s="18"/>
       <c r="I35" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F36" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="G36" s="18" t="s">
         <v>159</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>161</v>
       </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>3</v>
@@ -2256,73 +2256,73 @@
         <v>55</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G37" s="18" t="s">
         <v>54</v>
       </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="71.25">
       <c r="A38" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="G38" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="H38" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>168</v>
-      </c>
       <c r="I38" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28.5">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>206</v>
-      </c>
       <c r="H39" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:9">

--- a/QCM3_1_CH.xlsx
+++ b/QCM3_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6889125-5CFB-47B2-B5A6-386355AD4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A023E0-3094-4587-AF53-10DE18F07906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -295,9 +295,6 @@
     <t>⊖ Zn(s) | Zn²⁺(aq) || Cu²⁺(aq) | Cu(s) ⊕</t>
   </si>
   <si>
-    <t>⊖ Cu²⁺(aq) | Zn(s) || Zn²⁺(aq) | Cu(s) ⊕</t>
-  </si>
-  <si>
     <t>0,25 mol</t>
   </si>
   <si>
@@ -391,9 +388,6 @@
     <t>⊖ Fe(s) | Fe²⁺(aq) || Cu²⁺(aq) | Cu(s) ⊕</t>
   </si>
   <si>
-    <t>⊖ Cu²⁺(aq) | Cu(s) || Fe(s) | Fe²⁺(aq) ⊕</t>
-  </si>
-  <si>
     <t>Cu²⁺(aq) + 2e⁻ ⇌ Cu(s)  et  Fe(s) ⇌ Fe²⁺(aq) + 2e⁻</t>
   </si>
   <si>
@@ -445,9 +439,6 @@
     <t>Oxydation anodique : H₂(g) ⇌ 2H⁺(aq) + 2e⁻</t>
   </si>
   <si>
-    <t>Réduction cathodique : O₂(g) + 4H⁺(aq) + 4e⁻ ⇌ 2H₂O(l)</t>
-  </si>
-  <si>
     <t>Réduction cathodique : O₂(g) + 2e⁻ ⇌ 2H₂O(l)</t>
   </si>
   <si>
@@ -545,30 +536,6 @@
   </si>
   <si>
     <t>-525 mg</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La pile (Fer/Cuivre)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On réalise la pile suivante :
-• Un bécher contenant une solution aqueuse de sulfate de cuivre (Cu²⁺(aq) + SO₄²⁻(aq)) de concentration initiale C.
-• Un bécher contenant une solution aqueuse de sulfate de fer (Fe²⁺(aq) + SO₄²⁻(aq)) de même concentration initiale C.
-• Une lame de fer et une lame de cuivre.
-• Un pont salin.
-On relie les électrodes de la pile à un conducteur ohmique en série avec un ampèremètre. En fermant le circuit, l'ampèremètre indique le passage d'un courant électrique d'intensité constante I = 20 mA.
-Après une durée Δt de fonctionnement de la pile, on observe la formation d'un dépôt de cuivre sur l'électrode de cuivre et la diminution de la masse de l'électrode de fer.
-Données :
-- Masses molaires : M(Cu) = 63,5 g.mol⁻¹ et M(Fe) = 56 g.mol⁻¹
-- 1F = 9,65.10⁴ C.mol⁻¹</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La pile (Zinc/Cuivre)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On considère la pile (Zinc/Cuivre) schématisée dans la figure ci-contre.
-&lt;br&gt;Données :
-&lt;br&gt; * Masse de la partie immergée de l'électrode de Zinc : m = 6,54 g ; M(Zn) = 65,4 g.mol⁻¹
-&lt;br&gt; * Volume de chaque solution : V = 50 mL
-&lt;br&gt; * Concentration de chaque solution : C = 1,0 mol.L⁻¹
-&lt;br&gt; * 1F = 9,65.10⁴ C.mol⁻¹
-&lt;br&gt;On laisse fonctionner la pile pendant une durée Δt suffisamment longue jusqu'à ce que la pile ne débite plus.
-L'équation bilan du fonctionnement de cette pile est : Zn(s) + Cu²⁺(aq) → Zn²⁺(aq) + Cu(s)</t>
   </si>
   <si>
     <t>Le schéma conventionnel de cette pile est :</t>
@@ -605,9 +572,6 @@
   </si>
   <si>
     <t>L'équation de la réaction chimique à chaque électrode est :</t>
-  </si>
-  <si>
-    <t>La durée Δt du fonctionnement de la pile pour laquelle la masse de cuivre formée est m_forme = 31,75 mg :</t>
   </si>
   <si>
     <t xml:space="preserve"> La variation de la masse de fer est :</t>
@@ -732,6 +696,42 @@
 &lt;br&gt;La transformation est modélisée par l'équation chimique : 
 &lt;br&gt;$Cd^{2+}_{(aq)} + Fe_{(s)} \rightarrow Cd_{(s)} + Fe^{2+}_{(aq)}$.
 &lt;br&gt;On donne, à 25°C la constante de cette réaction : K = 20. $\quad$ $21 \times 0,90 = 19$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La pile (Zinc/Cuivre)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On considère la pile (Zinc/Cuivre) schématisée dans la figure ci-contre.
+&lt;br&gt;Données :
+&lt;br&gt; * Masse de la partie immergée de l'électrode de Zinc : m = 6,54 g ; M(Zn) = 65,4 g.mol⁻¹
+&lt;br&gt; * Volume de chaque solution : V = 50 mL
+&lt;br&gt; * Concentration de chaque solution : C = 1,0 mol.L⁻¹
+&lt;br&gt; * 1F = 9,65.10⁴ C.mol⁻¹
+&lt;br&gt;On laisse fonctionner la pile pendant une durée Δt suffisamment longue jusqu'à ce que la pile ne débite plus.
+&lt;br&gt;L'équation bilan du fonctionnement de cette pile est : Zn(s) + Cu²⁺(aq) → Zn²⁺(aq) + Cu(s)</t>
+  </si>
+  <si>
+    <t>⊕ Cu²⁺(aq) | Cu(s) || Zn(s) | Zn²⁺(aq) ⊖</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La pile (Fer/Cuivre)&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On réalise la pile suivante :
+&lt;br&gt;• Un bécher contenant une solution aqueuse de sulfate de cuivre (Cu²⁺(aq) + SO₄²⁻(aq)) de concentration initiale C.
+&lt;br&gt;• Un bécher contenant une solution aqueuse de sulfate de fer (Fe²⁺(aq) + SO₄²⁻(aq)) de même concentration initiale C.
+&lt;br&gt;• Une lame de fer et une lame de cuivre.
+&lt;br&gt;• Un pont salin.
+&lt;br&gt;On relie les électrodes de la pile à un conducteur ohmique en série avec un ampèremètre. En fermant le circuit, l'ampèremètre indique le passage d'un courant électrique d'intensité constante I = 20 mA.
+&lt;br&gt;Après une durée Δt de fonctionnement de la pile, on observe la formation d'un dépôt de cuivre sur l'électrode de cuivre et la diminution de la masse de l'électrode de fer.
+&lt;br&gt;Données :
+&lt;br&gt;- Masses molaires : M(Cu) = 63,5 g.mol⁻¹ $\quad$ et $\quad$ M(Fe) = 56 g.mol⁻¹
+&lt;br&gt;- 1F = 9,65.10⁴ C.mol⁻¹</t>
+  </si>
+  <si>
+    <t>⊕ Cu²⁺(aq) | Cu(s) || Fe(s) | Fe²⁺(aq) ⊖</t>
+  </si>
+  <si>
+    <t>La durée Δt du fonctionnement de la pile pour laquelle la masse de cuivre formée est m_{formée} = 31,75 mg :</t>
+  </si>
+  <si>
+    <t>Réduction cathodique : O₂(g) + 4H⁺(aq) + 2e⁻ ⇌ 2H₂O(l)</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -965,6 +965,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1317,7 +1320,7 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>65</v>
@@ -1427,7 +1430,7 @@
     </row>
     <row r="6" spans="1:11" ht="285">
       <c r="A6" s="11" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>70</v>
@@ -1452,7 +1455,7 @@
         <v>28</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K6" s="5"/>
     </row>
@@ -1539,7 +1542,7 @@
     </row>
     <row r="10" spans="1:11" ht="270.75">
       <c r="A10" s="11" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>74</v>
@@ -1645,7 +1648,7 @@
     </row>
     <row r="14" spans="1:11" ht="228">
       <c r="A14" s="11" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>80</v>
@@ -1705,10 +1708,10 @@
     </row>
     <row r="16" spans="1:11" ht="213.75">
       <c r="A16" s="11" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>3</v>
@@ -1723,531 +1726,531 @@
         <v>84</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
         <v>84</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="F17" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="G17" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>89</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="42.75">
       <c r="A18" s="15"/>
       <c r="B18" s="16" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="F18" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="G18" s="18" t="s">
         <v>92</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>93</v>
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="15"/>
       <c r="B19" s="16" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="F19" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="G19" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>97</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="F20" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>97</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="228">
       <c r="A21" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="F21" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="G21" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>101</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J21" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="F22" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="G22" s="18" t="s">
         <v>104</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>105</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.5">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="F23" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="G23" s="18" t="s">
         <v>108</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>109</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="F24" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="G24" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>113</v>
       </c>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="313.5">
       <c r="A25" s="11" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="14" t="s">
-        <v>116</v>
-      </c>
       <c r="G25" s="14" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.5">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="G26" s="18" t="s">
         <v>119</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>121</v>
       </c>
       <c r="H26" s="18"/>
       <c r="I26" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="42.75">
       <c r="A27" s="15"/>
       <c r="B27" s="16" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="G27" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="H27" s="18"/>
       <c r="I27" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="G28" s="18" t="s">
         <v>127</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>129</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="15"/>
       <c r="B29" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="G29" s="18" t="s">
         <v>131</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>133</v>
       </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="199.5">
       <c r="A30" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>137</v>
+      <c r="E30" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>132</v>
       </c>
       <c r="H30" s="14"/>
-      <c r="I30" s="14" t="s">
-        <v>136</v>
+      <c r="I30" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="J30" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.5">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>141</v>
       </c>
       <c r="H31" s="18"/>
       <c r="I31" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="28.5">
       <c r="A32" s="15"/>
       <c r="B32" s="16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>145</v>
       </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="15"/>
       <c r="B33" s="16" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>149</v>
       </c>
       <c r="H33" s="18"/>
       <c r="I33" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="185.25">
       <c r="A34" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="15"/>
       <c r="B35" s="16" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>155</v>
       </c>
       <c r="H35" s="18"/>
       <c r="I35" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="18" t="s">
         <v>156</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>159</v>
       </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>3</v>
@@ -2256,73 +2259,73 @@
         <v>55</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G37" s="18" t="s">
         <v>54</v>
       </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="71.25">
       <c r="A38" s="11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="H38" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="I38" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28.5">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:9">
